--- a/artfynd/A 26973-2026 artfynd.xlsx
+++ b/artfynd/A 26973-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043017</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043019</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,6 +1030,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043027</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1117,6 +1137,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665333</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1228,6 +1253,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043015</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1339,6 +1369,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043020</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1450,6 +1485,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043025</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1561,6 +1601,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043028</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1672,6 +1717,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043064</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1783,6 +1833,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043022</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1894,6 +1949,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043011</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2015,6 +2075,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043065</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2126,6 +2191,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043060</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2237,6 +2307,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043008</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2348,6 +2423,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043026</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2459,6 +2539,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043030</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2570,6 +2655,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043061</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2681,6 +2771,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043009</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2792,6 +2887,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043063</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2903,6 +3003,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043010</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3014,6 +3119,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043024</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3125,6 +3235,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043031</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3236,6 +3351,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043062</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3345,6 +3465,11 @@
       <c r="AY25" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043023</t>
         </is>
       </c>
     </row>
@@ -3462,6 +3587,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043066</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3573,6 +3703,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043013</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3684,8 +3819,42 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135043014</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 26973-2026 artfynd.xlsx
+++ b/artfynd/A 26973-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135043017</v>
       </c>
       <c r="B2" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>135043019</v>
       </c>
       <c r="B3" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>135043027</v>
       </c>
       <c r="B4" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>135043015</v>
       </c>
       <c r="B6" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>135043020</v>
       </c>
       <c r="B7" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>135043025</v>
       </c>
       <c r="B8" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>135043028</v>
       </c>
       <c r="B9" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>135043064</v>
       </c>
       <c r="B10" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>135043022</v>
       </c>
       <c r="B11" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>135043011</v>
       </c>
       <c r="B12" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>135043065</v>
       </c>
       <c r="B13" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>135043060</v>
       </c>
       <c r="B14" t="n">
-        <v>108205</v>
+        <v>108260</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>135043008</v>
       </c>
       <c r="B15" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>135043026</v>
       </c>
       <c r="B16" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>135043030</v>
       </c>
       <c r="B17" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>135043061</v>
       </c>
       <c r="B18" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>135043009</v>
       </c>
       <c r="B19" t="n">
-        <v>99001</v>
+        <v>99048</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>135043063</v>
       </c>
       <c r="B20" t="n">
-        <v>99001</v>
+        <v>99048</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>135043010</v>
       </c>
       <c r="B21" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>135043024</v>
       </c>
       <c r="B22" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>135043031</v>
       </c>
       <c r="B23" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>135043062</v>
       </c>
       <c r="B24" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         <v>135043023</v>
       </c>
       <c r="B25" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>135043066</v>
       </c>
       <c r="B26" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>135043013</v>
       </c>
       <c r="B27" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>135043014</v>
       </c>
       <c r="B28" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 26973-2026 artfynd.xlsx
+++ b/artfynd/A 26973-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135043017</v>
       </c>
       <c r="B2" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>135043019</v>
       </c>
       <c r="B3" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>135043027</v>
       </c>
       <c r="B4" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>135043015</v>
       </c>
       <c r="B6" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>135043020</v>
       </c>
       <c r="B7" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>135043025</v>
       </c>
       <c r="B8" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>135043028</v>
       </c>
       <c r="B9" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>135043064</v>
       </c>
       <c r="B10" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>135043022</v>
       </c>
       <c r="B11" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>135043011</v>
       </c>
       <c r="B12" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>135043060</v>
       </c>
       <c r="B14" t="n">
-        <v>108260</v>
+        <v>108287</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>135043008</v>
       </c>
       <c r="B15" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>135043026</v>
       </c>
       <c r="B16" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>135043030</v>
       </c>
       <c r="B17" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>135043061</v>
       </c>
       <c r="B18" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>135043009</v>
       </c>
       <c r="B19" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>135043063</v>
       </c>
       <c r="B20" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>135043010</v>
       </c>
       <c r="B21" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>135043024</v>
       </c>
       <c r="B22" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>135043031</v>
       </c>
       <c r="B23" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>135043062</v>
       </c>
       <c r="B24" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         <v>135043023</v>
       </c>
       <c r="B25" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>135043066</v>
       </c>
       <c r="B26" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>135043013</v>
       </c>
       <c r="B27" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>135043014</v>
       </c>
       <c r="B28" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
